--- a/output/graficos_regionales_migracion/plot_migracion_miginterna_2019_o_higgins_provincial.xlsx
+++ b/output/graficos_regionales_migracion/plot_migracion_miginterna_2019_o_higgins_provincial.xlsx
@@ -49,7 +49,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-27 23:09</t>
+    <t xml:space="preserve">2026-09-29 14:02</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_regionales_migracion/plot_migracion_miginterna_2019_o_higgins_provincial.xlsx
+++ b/output/graficos_regionales_migracion/plot_migracion_miginterna_2019_o_higgins_provincial.xlsx
@@ -49,7 +49,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-29 14:02</t>
+    <t xml:space="preserve">2026-09-29 18:36</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -504,7 +504,7 @@
         <v>3.96</v>
       </c>
       <c r="C3" s="2" t="n">
-        <v>32.49</v>
+        <v>32.48</v>
       </c>
       <c r="D3" s="2" t="n">
         <v>28.52</v>
@@ -518,10 +518,10 @@
         <v>0.66</v>
       </c>
       <c r="C4" s="2" t="n">
-        <v>25.85</v>
+        <v>25.84</v>
       </c>
       <c r="D4" s="2" t="n">
-        <v>25.18</v>
+        <v>25.19</v>
       </c>
     </row>
   </sheetData>

--- a/output/graficos_regionales_migracion/plot_migracion_miginterna_2019_o_higgins_provincial.xlsx
+++ b/output/graficos_regionales_migracion/plot_migracion_miginterna_2019_o_higgins_provincial.xlsx
@@ -49,7 +49,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-29 18:36</t>
+    <t xml:space="preserve">2026-10-05 04:01</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -504,10 +504,10 @@
         <v>3.96</v>
       </c>
       <c r="C3" s="2" t="n">
-        <v>32.48</v>
+        <v>32.49</v>
       </c>
       <c r="D3" s="2" t="n">
-        <v>28.52</v>
+        <v>28.53</v>
       </c>
     </row>
     <row r="4">
@@ -518,7 +518,7 @@
         <v>0.66</v>
       </c>
       <c r="C4" s="2" t="n">
-        <v>25.84</v>
+        <v>25.85</v>
       </c>
       <c r="D4" s="2" t="n">
         <v>25.19</v>
